--- a/ChargePoint_Model.xlsx
+++ b/ChargePoint_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanhi\CCTS_DATA\CCTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBF9923-50BD-478A-8F48-D0B8874A87F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E0914B-41E3-49CD-89B8-94F72587B341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
   <si>
     <t>Charge Point Model</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Core 150kW</t>
+  </si>
+  <si>
+    <t>BSS 12</t>
   </si>
 </sst>
 </file>
@@ -276,7 +279,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -573,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="72" bestFit="1" customWidth="1"/>
@@ -956,13 +969,25 @@
         <v>52</v>
       </c>
     </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A15180:A1048576 A1:A47">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1">
+  <conditionalFormatting sqref="A48">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>